--- a/Scrape PHEI/2026-05-Mei/Yield-Curve-13-Mei-2026.xlsx
+++ b/Scrape PHEI/2026-05-Mei/Yield-Curve-13-Mei-2026.xlsx
@@ -607,7 +607,7 @@
         <v>0.068284</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0689204301376749</v>
+        <v>0.06892043013767468</v>
       </c>
     </row>
     <row r="17">
@@ -673,7 +673,7 @@
         <v>0.068603</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06926574108290917</v>
+        <v>0.06926574108290939</v>
       </c>
     </row>
     <row r="23">
@@ -816,7 +816,7 @@
         <v>0.068666</v>
       </c>
       <c r="C35" t="n">
-        <v>0.06912975136476485</v>
+        <v>0.06912975136476462</v>
       </c>
     </row>
     <row r="36">

--- a/Scrape PHEI/2026-05-Mei/Yield-Curve-13-Mei-2026.xlsx
+++ b/Scrape PHEI/2026-05-Mei/Yield-Curve-13-Mei-2026.xlsx
@@ -607,7 +607,7 @@
         <v>0.068284</v>
       </c>
       <c r="C16" t="n">
-        <v>0.06892043013767468</v>
+        <v>0.0689204301376749</v>
       </c>
     </row>
     <row r="17">
@@ -673,7 +673,7 @@
         <v>0.068603</v>
       </c>
       <c r="C22" t="n">
-        <v>0.06926574108290939</v>
+        <v>0.06926574108290917</v>
       </c>
     </row>
     <row r="23">
@@ -816,7 +816,7 @@
         <v>0.068666</v>
       </c>
       <c r="C35" t="n">
-        <v>0.06912975136476462</v>
+        <v>0.06912975136476485</v>
       </c>
     </row>
     <row r="36">
